--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Italy Serie B_20242025.xlsx
@@ -18820,13 +18820,13 @@
         <v>11</v>
       </c>
       <c r="BA84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BB84" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC84" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BD84" t="n">
         <v>2</v>
@@ -19038,13 +19038,13 @@
         <v>10</v>
       </c>
       <c r="BA85" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BB85" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BC85" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BD85" t="n">
         <v>1.72</v>
@@ -19256,13 +19256,13 @@
         <v>5</v>
       </c>
       <c r="BA86" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BB86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC86" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BD86" t="n">
         <v>1.67</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Italy Serie B_20242025.xlsx
@@ -85719,13 +85719,13 @@
         <v>1.18</v>
       </c>
       <c r="AR391" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AS391" t="n">
         <v>1.23</v>
       </c>
       <c r="AT391" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AU391" t="n">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Italy Serie B_20242025.xlsx
@@ -84202,22 +84202,22 @@
         <v>2.75</v>
       </c>
       <c r="AU384" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV384" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW384" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX384" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY384" t="n">
         <v>6</v>
       </c>
-      <c r="AX384" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY384" t="n">
-        <v>8</v>
-      </c>
       <c r="AZ384" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA384" t="n">
         <v>1</v>
@@ -84426,16 +84426,16 @@
         <v>2</v>
       </c>
       <c r="AW385" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX385" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY385" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ385" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BA385" t="n">
         <v>3</v>
@@ -84644,16 +84644,16 @@
         <v>1</v>
       </c>
       <c r="AW386" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AX386" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY386" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AZ386" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA386" t="n">
         <v>6</v>
@@ -84847,31 +84847,31 @@
         <v>1.37</v>
       </c>
       <c r="AR387" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AS387" t="n">
         <v>1.15</v>
       </c>
       <c r="AT387" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="AU387" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV387" t="n">
         <v>4</v>
       </c>
-      <c r="AV387" t="n">
-        <v>3</v>
-      </c>
       <c r="AW387" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AX387" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY387" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AZ387" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA387" t="n">
         <v>2</v>
@@ -85283,13 +85283,13 @@
         <v>1.62</v>
       </c>
       <c r="AR389" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AS389" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AT389" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="AU389" t="n">
         <v>4</v>
